--- a/ACCY122/Assessment II/Calculation.xlsx
+++ b/ACCY122/Assessment II/Calculation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{945410A0-C7EC-4F97-A1BF-CA6EB19C4105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1A6650-145E-3D4C-951C-15AC2B4C78D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="122">
   <si>
     <t>Ref</t>
   </si>
@@ -282,9 +282,6 @@
     <t>Supplies (Used up)</t>
   </si>
   <si>
-    <t>drawings is an contra-equity account so it behaves like an expense account dr + / cr -</t>
-  </si>
-  <si>
     <t>INCOME</t>
   </si>
   <si>
@@ -387,10 +384,28 @@
     <t>TOTAL OWNER'S EQUITY</t>
   </si>
   <si>
-    <t>ADD: Profit for the month ended 31Aug25</t>
-  </si>
-  <si>
     <t>NET ASSETS (TA-TL)</t>
+  </si>
+  <si>
+    <t>ADD: Profit for the month ended 31 Aug25</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation  - Studio Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">s Payable </t>
+  </si>
+  <si>
+    <t>Capital  – Suzana P</t>
+  </si>
+  <si>
+    <t>Drawings  - Suzana P</t>
+  </si>
+  <si>
+    <t>drawings is an contra-equity  so it behaves like an expense  dr + / cr -</t>
+  </si>
+  <si>
+    <t>accum dep is an contra-asset  so dr - / cr +</t>
   </si>
 </sst>
 </file>
@@ -586,7 +601,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -600,37 +615,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -648,34 +648,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -689,9 +672,6 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -706,7 +686,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -715,48 +695,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -765,19 +711,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -793,6 +771,111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>117737</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD99440B-61A4-8BE0-0793-41B30EE3AC2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="431800" y="10604500"/>
+          <a:ext cx="7772400" cy="4842137"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>582950</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>243381</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>78750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBCC0BAD-01C6-AA63-E8D0-71B606CDE569}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9410491" y="4372132"/>
+          <a:ext cx="7800923" cy="1952520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1059,786 +1142,706 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" style="1"/>
-    <col min="4" max="4" width="71.5703125" style="1" customWidth="1"/>
-    <col min="5" max="9" width="9.140625" style="1"/>
-    <col min="10" max="10" width="69.7109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="3" width="9.1640625" style="1"/>
+    <col min="4" max="4" width="71.5" style="1" customWidth="1"/>
+    <col min="5" max="9" width="9.1640625" style="1"/>
+    <col min="10" max="10" width="69.6640625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
+    <row r="1" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="7"/>
-      <c r="H2" s="5" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="56"/>
+      <c r="H2" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="8" t="s">
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="56"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="8">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="7">
         <v>46235</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="1">
         <v>20000</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="H4" s="8">
+      <c r="F4" s="6"/>
+      <c r="H4" s="5">
         <v>1</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="7">
         <v>46265</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="1">
         <v>500</v>
       </c>
-      <c r="L4" s="10"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="8"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="13" t="s">
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="5"/>
+      <c r="D5" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10">
+      <c r="F5" s="6">
         <v>20000</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="13" t="s">
+      <c r="H5" s="5"/>
+      <c r="J5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="K5" s="9"/>
-      <c r="L5" s="10">
+      <c r="L5" s="6">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="14" t="s">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="5"/>
+      <c r="D6" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="14" t="s">
+      <c r="F6" s="6"/>
+      <c r="H6" s="5"/>
+      <c r="J6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="9"/>
-      <c r="L6" s="10"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="8">
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="5">
         <v>2</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="7">
         <v>46235</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="1">
         <v>3000</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="H7" s="8">
+      <c r="F7" s="6"/>
+      <c r="H7" s="5">
         <v>2</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="7">
         <v>46265</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="1">
         <v>700</v>
       </c>
-      <c r="L7" s="10"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="13" t="s">
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="5"/>
+      <c r="D8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10">
+      <c r="F8" s="6">
         <v>3000</v>
       </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="9"/>
-      <c r="J8" s="13" t="s">
+      <c r="H8" s="5"/>
+      <c r="J8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="10">
+      <c r="L8" s="6">
         <v>700</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="14" t="s">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="5"/>
+      <c r="D9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="14" t="s">
+      <c r="F9" s="6"/>
+      <c r="H9" s="5"/>
+      <c r="J9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="10"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="8">
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="5">
         <v>3</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="7">
         <v>46238</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="1">
         <v>1200</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="H10" s="8">
+      <c r="F10" s="6"/>
+      <c r="H10" s="5">
         <v>3</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="7">
         <v>46265</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="1">
         <v>200</v>
       </c>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="8"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="13" t="s">
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="5"/>
+      <c r="D11" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10">
+      <c r="F11" s="6">
         <v>1200</v>
       </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="15" t="s">
+      <c r="H11" s="5"/>
+      <c r="J11" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="10">
+      <c r="L11" s="6">
         <v>200</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="14" t="s">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="5"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="10"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="14" t="s">
+      <c r="F12" s="6"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="10"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="8">
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="5">
         <v>4</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="7">
         <v>46239</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="1">
         <v>12000</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="H13" s="8">
+      <c r="F13" s="6"/>
+      <c r="H13" s="5">
         <v>4</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="7">
         <v>46265</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="1">
         <v>1200</v>
       </c>
-      <c r="L13" s="10"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="13" t="s">
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="5"/>
+      <c r="D14" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="10">
+      <c r="F14" s="6">
         <v>4000</v>
       </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="13" t="s">
+      <c r="H14" s="5"/>
+      <c r="J14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="10">
+      <c r="L14" s="6">
         <v>1200</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="13" t="s">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="5"/>
+      <c r="D15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="10">
+      <c r="F15" s="6">
         <v>8000</v>
       </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="9"/>
-      <c r="J15" s="14" t="s">
+      <c r="H15" s="5"/>
+      <c r="J15" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="10"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="8"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="14" t="s">
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="5"/>
+      <c r="D16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="10"/>
-      <c r="H16" s="8">
+      <c r="F16" s="6"/>
+      <c r="H16" s="5">
         <v>5</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="7">
         <v>46265</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="J16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="1">
         <v>600</v>
       </c>
-      <c r="L16" s="10"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="8">
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="5">
         <v>5</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="7">
         <v>46242</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="1">
         <v>5500</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="13" t="s">
+      <c r="F17" s="6"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="10">
+      <c r="L17" s="6">
         <v>600</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="13" t="s">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="5"/>
+      <c r="D18" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="10">
+      <c r="F18" s="6">
         <v>5500</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="14" t="s">
+      <c r="H18" s="5"/>
+      <c r="J18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="10"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="14" t="s">
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="5"/>
+      <c r="D19" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="10"/>
-    </row>
-    <row r="20" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="8">
+      <c r="F19" s="6"/>
+      <c r="H19" s="5"/>
+      <c r="J19" s="2"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>6</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="7">
         <v>46246</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="1">
         <v>2200</v>
       </c>
-      <c r="F20" s="10"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="12" t="s">
+      <c r="F20" s="6"/>
+      <c r="H20" s="5"/>
+      <c r="J20" s="2" t="s">
         <v>33</v>
       </c>
       <c r="K20" s="4">
         <f>SUM(K4:K19)</f>
         <v>3200</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="14">
         <f>SUM(L4:L19)</f>
         <v>3200</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="8"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="13" t="s">
+    <row r="21" spans="2:12" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="D21" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="10">
+      <c r="F21" s="6">
         <v>2200</v>
       </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="20"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="8"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="14" t="s">
+      <c r="H21" s="11"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="15"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="5"/>
+      <c r="D22" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="10"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="8">
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="5">
         <v>7</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="7">
         <v>46249</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="1">
         <v>6000</v>
       </c>
-      <c r="F23" s="10"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="8"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="13" t="s">
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="5"/>
+      <c r="D24" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="10">
+      <c r="F24" s="6">
         <v>6000</v>
       </c>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="14" t="s">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="5"/>
+      <c r="D25" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="10"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="8">
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="5">
         <v>8</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="7">
         <v>46252</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="1">
         <v>5500</v>
       </c>
-      <c r="F26" s="10"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="8"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="13" t="s">
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="5"/>
+      <c r="D27" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10">
+      <c r="F27" s="6">
         <v>5500</v>
       </c>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="8"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="14" t="s">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="5"/>
+      <c r="D28" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="8">
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="5">
         <v>9</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="7">
         <v>46254</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="1">
         <v>3200</v>
       </c>
-      <c r="F29" s="10"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="8"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="13" t="s">
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="5"/>
+      <c r="D30" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="10">
+      <c r="F30" s="6">
         <v>3200</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="8"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="14" t="s">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="5"/>
+      <c r="D31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="10"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="8">
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="5">
         <v>10</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="7">
         <v>46256</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="1">
         <v>600</v>
       </c>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="8"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="13" t="s">
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B33" s="5"/>
+      <c r="D33" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="10">
+      <c r="F33" s="6">
         <v>600</v>
       </c>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="8"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="14" t="s">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="5"/>
+      <c r="D34" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="10"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="8">
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="5">
         <v>11</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="7">
         <v>46259</v>
       </c>
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="1">
         <v>2400</v>
       </c>
-      <c r="F35" s="10"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="8"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="13" t="s">
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B36" s="5"/>
+      <c r="D36" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="10">
+      <c r="F36" s="6">
         <v>2400</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="8"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="14" t="s">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B37" s="5"/>
+      <c r="D37" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="10"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="8">
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B38" s="5">
         <v>12</v>
       </c>
-      <c r="C38" s="11">
+      <c r="C38" s="7">
         <v>46260</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="1">
         <v>2200</v>
       </c>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="8"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="13" t="s">
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B39" s="5"/>
+      <c r="D39" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="10">
+      <c r="F39" s="6">
         <v>2200</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="8"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="14" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B40" s="5"/>
+      <c r="D40" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="10"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="8">
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B41" s="5">
         <v>13</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="7">
         <v>46262</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="1">
         <v>600</v>
       </c>
-      <c r="F41" s="10"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="8"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="12" t="s">
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B42" s="5"/>
+      <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="10">
+      <c r="F42" s="6">
         <v>600</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="8"/>
-      <c r="C43" s="9" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B43" s="5"/>
+      <c r="C43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="10"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="8">
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B44" s="5">
         <v>14</v>
       </c>
-      <c r="C44" s="11">
+      <c r="C44" s="7">
         <v>46265</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="1">
         <v>1000</v>
       </c>
-      <c r="F44" s="10"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="8"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="15" t="s">
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B45" s="5"/>
+      <c r="D45" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="10">
+      <c r="F45" s="6">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="8"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="14" t="s">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B46" s="5"/>
+      <c r="D46" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="10"/>
-    </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="8"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="10"/>
-    </row>
-    <row r="48" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="8"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="12" t="s">
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B47" s="5"/>
+      <c r="D47" s="2"/>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="5"/>
+      <c r="D48" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E48" s="4">
         <f>SUM(E4:E47)</f>
         <v>65400</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="14">
         <f>SUM(F4:F47)</f>
         <v>65400</v>
       </c>
     </row>
-    <row r="49" spans="2:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="16"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="20"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="11"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
+      <c r="E49" s="12"/>
+      <c r="F49" s="15"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D51" s="2"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B53" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="3" t="s">
         <v>46</v>
       </c>
@@ -1850,1181 +1853,1154 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA8E1411-F875-4BCF-A6DF-12BD20567178}">
-  <dimension ref="B1:O51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:O50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="6" max="6" width="5" customWidth="1"/>
-    <col min="8" max="8" width="40.5703125" customWidth="1"/>
-    <col min="11" max="11" width="4.140625" customWidth="1"/>
-    <col min="13" max="13" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="40.5" customWidth="1"/>
+    <col min="11" max="11" width="4.1640625" customWidth="1"/>
+    <col min="13" max="13" width="24.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="25" t="s">
+    <row r="1" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B2" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="27"/>
-      <c r="G2" s="40" t="s">
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="59"/>
+      <c r="G2" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-      <c r="L2" s="47" t="s">
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="29"/>
+      <c r="L2" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="42"/>
-    </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="29"/>
+    </row>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" t="s">
         <v>51</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" t="s">
         <v>51</v>
       </c>
-      <c r="N3" s="9" t="s">
+      <c r="N3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="10" t="s">
+      <c r="O3" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B4" s="30">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B4" s="18">
         <v>46235</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="32">
+      <c r="D4" s="20">
         <v>20000</v>
       </c>
-      <c r="E4" s="33"/>
-      <c r="G4" s="30">
+      <c r="E4" s="21"/>
+      <c r="G4" s="18">
         <v>46235</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33">
+      <c r="I4" s="20"/>
+      <c r="J4" s="21">
         <v>20000</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="18">
         <v>46242</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="33">
+      <c r="O4" s="21">
         <v>5500</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B5" s="30">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B5" s="18">
         <v>46235</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="33">
+      <c r="D5" s="20"/>
+      <c r="E5" s="21">
         <v>3000</v>
       </c>
-      <c r="G5" s="34">
+      <c r="G5" s="22">
         <v>46265</v>
       </c>
-      <c r="H5" s="31" t="s">
+      <c r="H5" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I5" s="32"/>
-      <c r="J5" s="33">
+      <c r="I5" s="20"/>
+      <c r="J5" s="21">
         <v>20000</v>
       </c>
-      <c r="L5" s="30">
+      <c r="L5" s="18">
         <v>46254</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="29"/>
-      <c r="O5" s="10">
+      <c r="O5" s="6">
         <v>3200</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="34">
+    <row r="6" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="22">
         <v>46239</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33">
+      <c r="D6" s="20"/>
+      <c r="E6" s="21">
         <v>4000</v>
       </c>
-      <c r="G6" s="36">
+      <c r="G6" s="24">
         <v>46266</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="44">
+      <c r="I6" s="30"/>
+      <c r="J6" s="31">
         <v>20000</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="22">
         <v>46265</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="10">
+      <c r="O6" s="6">
         <v>1200</v>
       </c>
     </row>
-    <row r="7" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="34">
+    <row r="7" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="22">
         <v>46246</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="33">
+      <c r="D7" s="20"/>
+      <c r="E7" s="21">
         <v>2200</v>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="22">
         <v>46265</v>
       </c>
-      <c r="M7" s="31" t="s">
+      <c r="M7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="N7" s="32"/>
-      <c r="O7" s="33">
+      <c r="N7" s="20"/>
+      <c r="O7" s="21">
         <v>9900</v>
       </c>
     </row>
-    <row r="8" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="34">
+    <row r="8" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="22">
         <v>46249</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="20">
         <v>6000</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="G8" s="47" t="s">
+      <c r="E8" s="21"/>
+      <c r="G8" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="H8" s="41"/>
-      <c r="I8" s="41"/>
-      <c r="J8" s="42"/>
-      <c r="L8" s="36">
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+      <c r="L8" s="24">
         <v>46266</v>
       </c>
-      <c r="M8" s="37" t="s">
+      <c r="M8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="43"/>
-      <c r="O8" s="44">
+      <c r="N8" s="30"/>
+      <c r="O8" s="31">
         <v>9900</v>
       </c>
     </row>
-    <row r="9" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="34">
+    <row r="9" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="22">
         <v>46252</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="20">
         <v>5500</v>
       </c>
-      <c r="E9" s="33"/>
-      <c r="G9" s="28" t="s">
+      <c r="E9" s="21"/>
+      <c r="G9" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" s="34">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B10" s="22">
         <v>46254</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="20">
         <v>3200</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="G10" s="30">
+      <c r="E10" s="21"/>
+      <c r="G10" s="18">
         <v>46238</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="10">
+      <c r="I10" s="20"/>
+      <c r="J10" s="6">
         <v>1200</v>
       </c>
-      <c r="L10" s="47" t="s">
+      <c r="L10" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="M10" s="41"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="42"/>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="30">
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="29"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B11" s="18">
         <v>46256</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33">
+      <c r="D11" s="20"/>
+      <c r="E11" s="21">
         <v>600</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="18">
         <v>46239</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="32"/>
-      <c r="J11" s="10">
+      <c r="I11" s="20"/>
+      <c r="J11" s="6">
         <v>8000</v>
       </c>
-      <c r="L11" s="28" t="s">
+      <c r="L11" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M11" s="29" t="s">
+      <c r="M11" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="9" t="s">
+      <c r="N11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O11" s="10" t="s">
+      <c r="O11" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="30">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B12" s="18">
         <v>46259</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="20">
         <v>2400</v>
       </c>
-      <c r="E12" s="33"/>
-      <c r="G12" s="30">
+      <c r="E12" s="21"/>
+      <c r="G12" s="18">
         <v>46262</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="20">
         <v>600</v>
       </c>
-      <c r="J12" s="33"/>
-      <c r="L12" s="30">
+      <c r="J12" s="21"/>
+      <c r="L12" s="18">
         <v>46249</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N12" s="29"/>
-      <c r="O12" s="10">
+      <c r="O12" s="6">
         <v>6000</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B13" s="30">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B13" s="18">
         <v>46260</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="10">
+      <c r="D13" s="20"/>
+      <c r="E13" s="6">
         <v>2200</v>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="22">
         <v>46265</v>
       </c>
-      <c r="H13" s="31" t="s">
+      <c r="H13" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="32"/>
-      <c r="J13" s="33">
+      <c r="I13" s="20"/>
+      <c r="J13" s="21">
         <v>8600</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="22">
         <v>46265</v>
       </c>
-      <c r="M13" s="31" t="s">
+      <c r="M13" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="N13" s="32"/>
-      <c r="O13" s="10">
+      <c r="N13" s="20"/>
+      <c r="O13" s="6">
         <v>6000</v>
       </c>
     </row>
-    <row r="14" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="30">
+    <row r="14" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="18">
         <v>46262</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="32"/>
-      <c r="E14" s="10">
+      <c r="D14" s="20"/>
+      <c r="E14" s="6">
         <v>600</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="24">
         <v>46266</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="38"/>
-      <c r="J14" s="44">
+      <c r="I14" s="25"/>
+      <c r="J14" s="31">
         <v>8600</v>
       </c>
-      <c r="L14" s="36">
+      <c r="L14" s="24">
         <v>46266</v>
       </c>
-      <c r="M14" s="37" t="s">
+      <c r="M14" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="43"/>
-      <c r="O14" s="20">
+      <c r="N14" s="30"/>
+      <c r="O14" s="15">
         <v>6000</v>
       </c>
     </row>
-    <row r="15" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="30">
+    <row r="15" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18">
         <v>46265</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="32"/>
-      <c r="E15" s="10">
+      <c r="D15" s="20"/>
+      <c r="E15" s="6">
         <v>1000</v>
       </c>
-      <c r="G15" s="45"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B16" s="34">
+      <c r="G15" s="32"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B16" s="22">
         <v>46265</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33">
+      <c r="D16" s="20"/>
+      <c r="E16" s="21">
         <v>23500</v>
       </c>
-      <c r="G16" s="47" t="s">
+      <c r="G16" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="42"/>
-      <c r="L16" s="40" t="s">
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="29"/>
+      <c r="L16" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="42"/>
-    </row>
-    <row r="17" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="24">
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="29"/>
+    </row>
+    <row r="17" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="17"/>
+      <c r="D17" s="16">
         <f>SUM(D4:D16)</f>
         <v>37100</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="23">
         <f>SUM(E4:E16)</f>
         <v>37100</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="G17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" t="s">
         <v>51</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L17" s="28" t="s">
+      <c r="L17" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M17" s="29" t="s">
+      <c r="M17" t="s">
         <v>51</v>
       </c>
-      <c r="N17" s="9" t="s">
+      <c r="N17" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O17" s="10" t="s">
+      <c r="O17" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="36">
+    <row r="18" spans="2:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="24">
         <v>46266</v>
       </c>
-      <c r="C18" s="37" t="s">
+      <c r="C18" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="38">
+      <c r="D18" s="25">
         <v>23500</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="G18" s="30">
+      <c r="E18" s="26"/>
+      <c r="G18" s="18">
         <v>46242</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18">
         <v>5500</v>
       </c>
-      <c r="J18" s="48"/>
-      <c r="L18" s="46">
+      <c r="J18" s="35"/>
+      <c r="L18" s="33">
         <v>46256</v>
       </c>
-      <c r="M18" s="18" t="s">
+      <c r="M18" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="N18" s="38">
+      <c r="N18" s="25">
         <v>600</v>
       </c>
-      <c r="O18" s="39"/>
-    </row>
-    <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G19" s="46">
+      <c r="O18" s="26"/>
+    </row>
+    <row r="19" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G19" s="33">
         <v>46252</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="44">
+      <c r="I19" s="30"/>
+      <c r="J19" s="31">
         <v>5500</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="40" t="s">
+    <row r="20" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="41"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="42"/>
-      <c r="L20" s="47" t="s">
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="L20" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="42"/>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="29"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B21" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>51</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="42"/>
-      <c r="L21" s="28" t="s">
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="29"/>
+      <c r="L21" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M21" s="29" t="s">
+      <c r="M21" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="9" t="s">
+      <c r="N21" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O21" s="10" t="s">
+      <c r="O21" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="30">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B22" s="18">
         <v>46235</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="20">
         <v>3000</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="G22" s="28" t="s">
+      <c r="E22" s="21"/>
+      <c r="G22" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="H22" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L22" s="30">
+      <c r="L22" s="18">
         <v>46259</v>
       </c>
-      <c r="M22" s="12" t="s">
+      <c r="M22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="10">
+      <c r="N22" s="1"/>
+      <c r="O22" s="6">
         <v>2400</v>
       </c>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="34">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B23" s="22">
         <v>46265</v>
       </c>
-      <c r="C23" s="12" t="s">
+      <c r="C23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="32"/>
-      <c r="E23" s="10">
+      <c r="D23" s="20"/>
+      <c r="E23" s="6">
         <v>500</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="18">
         <v>46246</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23">
         <v>2200</v>
       </c>
-      <c r="J23" s="48"/>
-      <c r="L23" s="34">
+      <c r="J23" s="35"/>
+      <c r="L23" s="22">
         <v>46265</v>
       </c>
-      <c r="M23" s="12" t="s">
+      <c r="M23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="N23" s="32">
+      <c r="N23" s="20">
         <v>1200</v>
       </c>
-      <c r="O23" s="33"/>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="34">
+      <c r="O23" s="21"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B24" s="22">
         <v>46265</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33">
+      <c r="D24" s="20"/>
+      <c r="E24" s="21">
         <v>2500</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="18">
         <v>46260</v>
       </c>
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24">
         <v>2200</v>
       </c>
-      <c r="J24" s="48"/>
-      <c r="L24" s="34">
+      <c r="J24" s="35"/>
+      <c r="L24" s="22">
         <v>46265</v>
       </c>
-      <c r="M24" s="31" t="s">
+      <c r="M24" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="20">
         <v>1200</v>
       </c>
-      <c r="O24" s="33"/>
-    </row>
-    <row r="25" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="28"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="24">
+      <c r="O24" s="21"/>
+    </row>
+    <row r="25" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="17"/>
+      <c r="D25" s="16">
         <v>3000</v>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="23">
         <v>3000</v>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="22">
         <v>46265</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25">
         <v>600</v>
       </c>
-      <c r="J25" s="48"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="29"/>
-      <c r="N25" s="24">
+      <c r="J25" s="35"/>
+      <c r="L25" s="17"/>
+      <c r="N25" s="16">
         <v>2400</v>
       </c>
-      <c r="O25" s="35">
+      <c r="O25" s="23">
         <v>2400</v>
       </c>
     </row>
-    <row r="26" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="36">
+    <row r="26" spans="2:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="24">
         <v>46266</v>
       </c>
-      <c r="C26" s="37" t="s">
+      <c r="C26" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="38">
+      <c r="D26" s="25">
         <v>2500</v>
       </c>
-      <c r="E26" s="44"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="50">
+      <c r="E26" s="31"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="37">
         <v>5000</v>
       </c>
-      <c r="J26" s="39"/>
-      <c r="L26" s="36">
+      <c r="J26" s="26"/>
+      <c r="L26" s="24">
         <v>46266</v>
       </c>
-      <c r="M26" s="37" t="s">
+      <c r="M26" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N26" s="38"/>
-      <c r="O26" s="44">
+      <c r="N26" s="25"/>
+      <c r="O26" s="31">
         <v>1200</v>
       </c>
     </row>
-    <row r="27" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
+    <row r="27" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B28" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="41"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="42"/>
-      <c r="G28" s="47" t="s">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="29"/>
+      <c r="G28" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="42"/>
-      <c r="L28" s="47" t="s">
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="29"/>
+      <c r="L28" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="M28" s="41"/>
-      <c r="N28" s="41"/>
-      <c r="O28" s="42"/>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B29" s="28" t="s">
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="29"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B29" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H29" s="29" t="s">
+      <c r="H29" t="s">
         <v>51</v>
       </c>
-      <c r="I29" s="9" t="s">
+      <c r="I29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L29" s="28" t="s">
+      <c r="L29" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M29" s="29" t="s">
+      <c r="M29" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="9" t="s">
+      <c r="N29" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O29" s="10" t="s">
+      <c r="O29" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B30" s="30">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B30" s="18">
         <v>46238</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="C30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="1">
         <v>1200</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="G30" s="34">
+      <c r="E30" s="21"/>
+      <c r="G30" s="22">
         <v>46265</v>
       </c>
-      <c r="H30" s="29" t="s">
+      <c r="H30" t="s">
         <v>22</v>
       </c>
-      <c r="I30" s="29"/>
-      <c r="J30" s="33">
+      <c r="J30" s="21">
         <v>600</v>
       </c>
-      <c r="L30" s="30">
+      <c r="L30" s="18">
         <v>46265</v>
       </c>
-      <c r="M30" s="29" t="s">
+      <c r="M30" t="s">
         <v>10</v>
       </c>
-      <c r="N30" s="32">
+      <c r="N30" s="20">
         <v>1000</v>
       </c>
-      <c r="O30" s="48"/>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B31" s="34">
+      <c r="O30" s="35"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B31" s="22">
         <v>46265</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="32"/>
-      <c r="E31" s="10">
+      <c r="D31" s="20"/>
+      <c r="E31" s="6">
         <v>700</v>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="22">
         <v>46265</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I31" s="29"/>
-      <c r="J31" s="33">
+      <c r="J31" s="21">
         <v>600</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="22">
         <v>46265</v>
       </c>
-      <c r="M31" s="31" t="s">
+      <c r="M31" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="N31" s="32">
+      <c r="N31" s="20">
         <v>1000</v>
       </c>
-      <c r="O31" s="48"/>
-    </row>
-    <row r="32" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="34">
+      <c r="O31" s="35"/>
+    </row>
+    <row r="32" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="22">
         <v>46265</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="33">
+      <c r="D32" s="20"/>
+      <c r="E32" s="21">
         <v>500</v>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="24">
         <v>46266</v>
       </c>
-      <c r="H32" s="37" t="s">
+      <c r="H32" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I32" s="43"/>
-      <c r="J32" s="44">
+      <c r="I32" s="30"/>
+      <c r="J32" s="31">
         <v>600</v>
       </c>
-      <c r="L32" s="36">
+      <c r="L32" s="24">
         <v>46266</v>
       </c>
-      <c r="M32" s="37" t="s">
+      <c r="M32" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="N32" s="38">
+      <c r="N32" s="25">
         <v>1000</v>
       </c>
-      <c r="O32" s="39"/>
-    </row>
-    <row r="33" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="24">
+      <c r="O32" s="26"/>
+    </row>
+    <row r="33" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="17"/>
+      <c r="D33" s="16">
         <v>1200</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="23">
         <v>1200</v>
       </c>
     </row>
-    <row r="34" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="36">
+    <row r="34" spans="2:15" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="24">
         <v>46266</v>
       </c>
-      <c r="C34" s="37" t="s">
+      <c r="C34" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="38">
+      <c r="D34" s="25">
         <v>500</v>
       </c>
-      <c r="E34" s="44"/>
-      <c r="G34" s="40" t="s">
+      <c r="E34" s="31"/>
+      <c r="G34" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="42"/>
-      <c r="L34" s="40" t="s">
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="29"/>
+      <c r="L34" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="M34" s="41"/>
-      <c r="N34" s="41"/>
-      <c r="O34" s="42"/>
-    </row>
-    <row r="35" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G35" s="28" t="s">
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="29"/>
+    </row>
+    <row r="35" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G35" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H35" s="29" t="s">
+      <c r="H35" t="s">
         <v>51</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J35" s="10" t="s">
+      <c r="J35" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L35" s="28" t="s">
+      <c r="L35" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M35" s="29" t="s">
+      <c r="M35" t="s">
         <v>51</v>
       </c>
-      <c r="N35" s="9" t="s">
+      <c r="N35" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O35" s="10" t="s">
+      <c r="O35" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="36" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="40" t="s">
+    <row r="36" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="41"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="G36" s="46">
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
+      <c r="G36" s="33">
         <v>46265</v>
       </c>
-      <c r="H36" s="43" t="s">
+      <c r="H36" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="12">
         <v>200</v>
       </c>
-      <c r="J36" s="44"/>
-      <c r="L36" s="36">
+      <c r="J36" s="31"/>
+      <c r="L36" s="24">
         <v>46265</v>
       </c>
-      <c r="M36" s="18" t="s">
+      <c r="M36" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="N36" s="17">
+      <c r="N36" s="12">
         <v>500</v>
       </c>
-      <c r="O36" s="39"/>
-    </row>
-    <row r="37" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="28" t="s">
+      <c r="O36" s="26"/>
+    </row>
+    <row r="37" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B38" s="30">
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B38" s="18">
         <v>46239</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="1">
         <v>4000</v>
       </c>
-      <c r="E38" s="33"/>
-      <c r="G38" s="40" t="s">
+      <c r="E38" s="21"/>
+      <c r="G38" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="42"/>
-      <c r="L38" s="40" t="s">
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="29"/>
+      <c r="L38" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="42"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B39" s="30">
+      <c r="M38" s="28"/>
+      <c r="N38" s="28"/>
+      <c r="O38" s="29"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B39" s="18">
         <v>46239</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="20">
         <v>8000</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="G39" s="28" t="s">
+      <c r="E39" s="6"/>
+      <c r="G39" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H39" s="29" t="s">
+      <c r="H39" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="9" t="s">
+      <c r="I39" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="J39" s="10" t="s">
+      <c r="J39" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="L39" s="28" t="s">
+      <c r="L39" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="M39" s="29" t="s">
+      <c r="M39" t="s">
         <v>51</v>
       </c>
-      <c r="N39" s="9" t="s">
+      <c r="N39" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="O39" s="10" t="s">
+      <c r="O39" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="34">
+    <row r="40" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="22">
         <v>46265</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="20">
         <v>12000</v>
       </c>
-      <c r="E40" s="33"/>
-      <c r="G40" s="30">
+      <c r="E40" s="21"/>
+      <c r="G40" s="18">
         <v>46265</v>
       </c>
-      <c r="H40" s="29" t="s">
+      <c r="H40" t="s">
         <v>71</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="1">
         <v>200</v>
       </c>
-      <c r="J40" s="33"/>
-      <c r="L40" s="36">
+      <c r="J40" s="21"/>
+      <c r="L40" s="24">
         <v>46265</v>
       </c>
-      <c r="M40" s="18" t="s">
+      <c r="M40" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="N40" s="17">
+      <c r="N40" s="12">
         <v>700</v>
       </c>
-      <c r="O40" s="39"/>
-    </row>
-    <row r="41" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="36">
+      <c r="O40" s="26"/>
+    </row>
+    <row r="41" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="24">
         <v>46266</v>
       </c>
-      <c r="C41" s="37" t="s">
+      <c r="C41" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="38">
+      <c r="D41" s="25">
         <v>12000</v>
       </c>
-      <c r="E41" s="44"/>
-      <c r="G41" s="34">
+      <c r="E41" s="31"/>
+      <c r="G41" s="22">
         <v>46265</v>
       </c>
-      <c r="H41" s="31" t="s">
+      <c r="H41" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="20">
         <v>200</v>
       </c>
-      <c r="J41" s="33"/>
-    </row>
-    <row r="42" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="G42" s="36">
+      <c r="J41" s="21"/>
+    </row>
+    <row r="42" spans="2:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="G42" s="24">
         <v>46266</v>
       </c>
-      <c r="H42" s="37" t="s">
+      <c r="H42" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="I42" s="38">
+      <c r="I42" s="25">
         <v>200</v>
       </c>
-      <c r="J42" s="44"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G43" s="45"/>
-      <c r="H43" s="31"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="32"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="G44" s="45"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="32"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="J42" s="31"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="G43" s="32"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="G44" s="32"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B46" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B47" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="B48" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B47" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="32"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="45"/>
-      <c r="C49" s="31"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="45"/>
-      <c r="C50" s="23"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B49" s="32"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B50" s="32"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3037,240 +3013,211 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2483F31C-F792-48EB-B93F-5257B81B8823}">
   <dimension ref="B1:E26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="49.5703125" customWidth="1"/>
+    <col min="2" max="2" width="49.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="55" t="s">
+    <row r="1" spans="2:5" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B2" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="22"/>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="59" t="s">
+      <c r="C2" s="52"/>
+      <c r="D2" s="53"/>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="60" t="s">
+      <c r="C3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="61" t="s">
+      <c r="D3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="32">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B4" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="20">
         <v>23500</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="29"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="52" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="32">
+      <c r="D4" s="21"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B5" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="20">
         <v>2500</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="29"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="52" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="D5" s="21"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B6" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="20">
         <v>500</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="29"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="32">
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="20">
         <v>12000</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="29"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="32">
+      <c r="D7" s="21"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B8" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="20">
         <v>500</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="29"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="32">
+      <c r="D8" s="21"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B9" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="20">
         <v>700</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="29"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="32">
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="20">
         <v>600</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="29"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="32">
+      <c r="D10" s="21"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B11" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="20">
         <v>5000</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="29"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="52" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="32">
+      <c r="D11" s="21"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="20">
         <v>200</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="29"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33">
+      <c r="D12" s="21"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21">
         <v>200</v>
       </c>
-      <c r="E13" s="29"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="33">
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B14" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21">
         <v>8600</v>
       </c>
-      <c r="E14" s="29"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="53">
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B15" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="21">
         <v>600</v>
       </c>
-      <c r="E15" s="29"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33">
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B16" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="21">
         <v>1200</v>
       </c>
-      <c r="E16" s="29"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="33">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="21">
         <v>9900</v>
       </c>
-      <c r="E17" s="29"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="33">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="17" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="21">
         <v>6000</v>
       </c>
-      <c r="E18" s="29"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="33">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="21">
         <v>20000</v>
       </c>
-      <c r="E19" s="29"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="32">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="20">
         <v>1000</v>
       </c>
-      <c r="D20" s="33"/>
-      <c r="E20" s="29"/>
-    </row>
-    <row r="21" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="28"/>
-      <c r="C21" s="24">
+      <c r="D20" s="21"/>
+    </row>
+    <row r="21" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="17"/>
+      <c r="C21" s="16">
         <f>SUM(C4:C20)</f>
         <v>46500</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="23">
         <f>SUM(D4:D19)</f>
         <v>46500</v>
       </c>
-      <c r="E21" s="29"/>
-    </row>
-    <row r="22" spans="2:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="54"/>
-      <c r="C22" s="38"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="29"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="12"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="29"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="2:4" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="39"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="31"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" s="3" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3284,150 +3231,123 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE339C66-3CA4-4739-A6A3-BB056C0B94A4}">
   <dimension ref="B1:F15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="7.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="62" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="58" t="s">
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="40" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="21">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="17"/>
+      <c r="F6" s="35"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="48"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="28" t="s">
+      <c r="F7" s="35"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="20">
+        <v>200</v>
+      </c>
+      <c r="F8" s="35"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="33">
-        <v>9900</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="48"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="48"/>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="68" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="32">
-        <v>200</v>
-      </c>
-      <c r="F8" s="48"/>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="68" t="s">
+      <c r="E9" s="20">
+        <v>500</v>
+      </c>
+      <c r="F9" s="35"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="32">
-        <v>500</v>
-      </c>
-      <c r="F9" s="48"/>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="68" t="s">
+      <c r="E10" s="20">
+        <v>700</v>
+      </c>
+      <c r="F10" s="35"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="32">
-        <v>700</v>
-      </c>
-      <c r="F10" s="48"/>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="68" t="s">
+      <c r="E11" s="20">
+        <v>600</v>
+      </c>
+      <c r="F11" s="35"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="32">
-        <v>600</v>
-      </c>
-      <c r="F11" s="48"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="32">
+      <c r="E12" s="20">
         <v>5000</v>
       </c>
-      <c r="F12" s="48"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="69" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="66">
+      <c r="F12" s="35"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="42"/>
+      <c r="F13" s="41">
         <f>SUM(E8:E12)</f>
         <v>7000</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="70" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="66">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="45" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="41">
         <v>2900</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="49"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="39"/>
+    <row r="15" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="36"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3441,352 +3361,263 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F75FFC87-7B79-4AF4-90E9-13BD22AE4B86}">
   <dimension ref="B1:H36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="35.85546875" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="55" t="s">
+    <row r="1" spans="2:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B2" s="51" t="s">
+        <v>91</v>
+      </c>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="53"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B3" s="48" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="57"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="62" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="64"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="28" t="s">
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="50"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B4" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="35"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B5" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="48"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="28" t="s">
+      <c r="F5" s="21">
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B6" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="21">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B7" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="21">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B8" s="38"/>
+      <c r="F8" s="21"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B9" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="33">
-        <v>23500</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="52" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="33">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="52" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="33">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="52"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="33"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="33">
+      <c r="F9" s="21">
         <f>SUM(F5:F7)</f>
         <v>26500</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="33"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B11" s="65" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="29"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="33"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B12" s="52" t="s">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B10" s="17"/>
+      <c r="F10" s="21"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="20">
+        <v>12000</v>
+      </c>
+      <c r="F12" s="35"/>
+      <c r="H12" s="20"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="20">
+        <v>200</v>
+      </c>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B15" s="38"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B16" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="32">
-        <v>12000</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="H12" s="51"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="32">
-        <v>200</v>
-      </c>
-      <c r="F13" s="53"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B14" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="53">
-        <v>11800</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B15" s="65"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="53"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B16" s="70" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="72">
+      <c r="F16" s="47">
         <f>F9+F14</f>
         <v>38300</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="48"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="65" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="48"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="17"/>
+      <c r="F17" s="35"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" s="35"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="21">
+        <v>8600</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="33">
-        <v>8600</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="28" t="s">
+      <c r="F20" s="21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="53">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
+      <c r="F21" s="21">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="33">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="74" t="s">
+      <c r="F22" s="21">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B23" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="33">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="74" t="s">
-        <v>101</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="33">
+      <c r="F23" s="21">
         <f>SUM(F19:F22)</f>
         <v>16400</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="74"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="33"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="65" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="33"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="65"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="33"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="70" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="72">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="17"/>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B25" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B26" s="38"/>
+      <c r="F26" s="21"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" s="47">
         <f>F25+F23</f>
         <v>16400</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="48"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="58" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="72">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="17"/>
+      <c r="F28" s="35"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F29" s="47">
         <f>F16-F27</f>
         <v>21900</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="48"/>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="28" t="s">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B30" s="17"/>
+      <c r="F30" s="35"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="35"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B32" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="20">
+        <v>20000</v>
+      </c>
+      <c r="F32" s="35"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B33" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="20">
+        <v>2900</v>
+      </c>
+      <c r="F33" s="35"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E34" s="20">
+        <v>1000</v>
+      </c>
+      <c r="F34" s="35"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="48"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="32">
-        <v>20000</v>
-      </c>
-      <c r="F32" s="48"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="32">
-        <v>2900</v>
-      </c>
-      <c r="F33" s="48"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="32">
-        <v>-1000</v>
-      </c>
-      <c r="F34" s="48"/>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="58" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="72">
+      <c r="F35" s="47">
         <v>21900</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="49"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="39"/>
+    <row r="36" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="36"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="2">
